--- a/htr-FHIR/ig/mappingSystemeFHIR.xlsx
+++ b/htr-FHIR/ig/mappingSystemeFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T13:52:25+00:00</t>
+    <t>2025-03-25T14:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingSystemeFHIR.xlsx
+++ b/htr-FHIR/ig/mappingSystemeFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T14:07:20+00:00</t>
+    <t>2025-03-31T09:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingSystemeFHIR.xlsx
+++ b/htr-FHIR/ig/mappingSystemeFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T09:17:15+00:00</t>
+    <t>2025-04-14T15:21:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingSystemeFHIR.xlsx
+++ b/htr-FHIR/ig/mappingSystemeFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-14T15:21:44+00:00</t>
+    <t>2025-04-23T09:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingSystemeFHIR.xlsx
+++ b/htr-FHIR/ig/mappingSystemeFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:31:53+00:00</t>
+    <t>2025-04-24T14:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingSystemeFHIR.xlsx
+++ b/htr-FHIR/ig/mappingSystemeFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T14:52:25+00:00</t>
+    <t>2025-04-28T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingSystemeFHIR.xlsx
+++ b/htr-FHIR/ig/mappingSystemeFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:47:42+00:00</t>
+    <t>2025-04-28T07:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingSystemeFHIR.xlsx
+++ b/htr-FHIR/ig/mappingSystemeFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:48:19+00:00</t>
+    <t>2025-04-28T09:06:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
